--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.51311001912002</v>
+        <v>3.983380378107003</v>
       </c>
       <c r="D2" t="n">
-        <v>24.72206350720197</v>
+        <v>4.017335319920321</v>
       </c>
       <c r="E2" t="n">
-        <v>9.123816738132561</v>
+        <v>1.482620219946541</v>
       </c>
       <c r="F2" t="n">
-        <v>9.142634372458849</v>
+        <v>1.485678085524563</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.22665097506759</v>
+        <v>6.211830783448483</v>
       </c>
       <c r="D3" t="n">
-        <v>38.04343515687067</v>
+        <v>6.182058212991485</v>
       </c>
       <c r="E3" t="n">
-        <v>9.123816738132561</v>
+        <v>1.482620219946541</v>
       </c>
       <c r="F3" t="n">
-        <v>9.142634372458849</v>
+        <v>1.485678085524563</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.08653374443692</v>
+        <v>5.701561733470999</v>
       </c>
       <c r="D4" t="n">
-        <v>35.19540028871203</v>
+        <v>5.719252546915705</v>
       </c>
       <c r="E4" t="n">
-        <v>9.123816738132561</v>
+        <v>1.482620219946541</v>
       </c>
       <c r="F4" t="n">
-        <v>9.142634372458849</v>
+        <v>1.485678085524563</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.74960643015984</v>
+        <v>5.809311044900975</v>
       </c>
       <c r="D5" t="n">
-        <v>35.5399328989029</v>
+        <v>5.775239096071722</v>
       </c>
       <c r="E5" t="n">
-        <v>9.123816738132561</v>
+        <v>1.482620219946541</v>
       </c>
       <c r="F5" t="n">
-        <v>9.142634372458849</v>
+        <v>1.485678085524563</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.73488431332903</v>
+        <v>6.619418700915967</v>
       </c>
       <c r="D6" t="n">
-        <v>40.78003307016141</v>
+        <v>6.626755373901229</v>
       </c>
       <c r="E6" t="n">
-        <v>9.123816738132561</v>
+        <v>1.482620219946541</v>
       </c>
       <c r="F6" t="n">
-        <v>9.142634372458849</v>
+        <v>1.485678085524563</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.53431786102484</v>
+        <v>4.636826652416536</v>
       </c>
       <c r="D7" t="n">
-        <v>28.60038306651077</v>
+        <v>4.647562248308001</v>
       </c>
       <c r="E7" t="n">
-        <v>9.123816738132561</v>
+        <v>1.482620219946541</v>
       </c>
       <c r="F7" t="n">
-        <v>9.142634372458849</v>
+        <v>1.485678085524563</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.32443922244992</v>
+        <v>2.002721373648113</v>
       </c>
       <c r="D8" t="n">
-        <v>12.10417819512756</v>
+        <v>1.966928956708229</v>
       </c>
       <c r="E8" t="n">
-        <v>9.123816738132561</v>
+        <v>1.482620219946541</v>
       </c>
       <c r="F8" t="n">
-        <v>9.142634372458849</v>
+        <v>1.485678085524563</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
